--- a/models/pt_sl_grid.xlsx
+++ b/models/pt_sl_grid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,19 +465,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.189364172588361</v>
+        <v>0.5024972746637232</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6718870465839951</v>
+        <v>0.00872563731817788</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1387487808276439</v>
+        <v>0.488777088018099</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -488,19 +488,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1900608425061539</v>
+        <v>0.6077203417275211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7099252240954902</v>
+        <v>0.03090234857849197</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1000139333983559</v>
+        <v>0.3613773096939869</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -511,19 +511,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1903952440666945</v>
+        <v>0.6595131340682999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.738172867028935</v>
+        <v>0.06474669196630162</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07143188890437044</v>
+        <v>0.2757401739653985</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -534,19 +534,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1384329571315777</v>
+        <v>0.6854756681064956</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7216478565788863</v>
+        <v>0.1059118131354367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.139919186289536</v>
+        <v>0.2086125187580677</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -557,19 +557,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1389624262691004</v>
+        <v>0.697877658628255</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7600575913798708</v>
+        <v>0.1472456998982845</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1009799823510287</v>
+        <v>0.1548766414734605</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -580,19 +580,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1391760717105569</v>
+        <v>0.7034788518466148</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7887418141284659</v>
+        <v>0.1817970342867829</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07208211416097719</v>
+        <v>0.1147241138666022</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -603,19 +603,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1017788305234313</v>
+        <v>0.3717586743234552</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7577632251172728</v>
+        <v>0.03185564612135615</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1404579443592959</v>
+        <v>0.5963856795551886</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -626,19 +626,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1021596767451581</v>
+        <v>0.4615054803205634</v>
       </c>
       <c r="E9" t="n">
-        <v>0.796544517207747</v>
+        <v>0.08526311468306277</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1012958060470949</v>
+        <v>0.4532314049963738</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -649,21 +649,642 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.102308299660954</v>
+        <v>0.5067392206678556</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8253587850076634</v>
+        <v>0.1483312731767614</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07233291533138266</v>
+        <v>0.3449295061553829</v>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5286376967601567</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2123937803036869</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2589685229361564</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5390920411058252</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.2700523173340509</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1908556415601239</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5438539675878835</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3155734153138812</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1405726170982353</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.2796491500143679</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.06933529162238471</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6510155583632474</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3489981253335401</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1522174430644183</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4987844316020416</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3831663162119878</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2367188319596422</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.38011485182837</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3990987005049284</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3158242830883191</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2850770164067524</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.4069713873900173</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3834035002896383</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2096251123203445</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.4105975670387112</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.435168925236842</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1542335077244468</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2123071168906992</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1115312512828466</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6761616318264543</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.262726978320463</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2169869411920324</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5202860804875045</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.2869744890279558</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3164582943728078</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3965672165992364</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.2985463352779387</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4041616683163123</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.297291996405749</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.3044166411997865</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.4767810471677028</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2188023116325106</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3071396968605039</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5319765187763126</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.1608837843631836</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1579144221602908</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1531570569104949</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.6889285209292142</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1936562381693038</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2752475608810476</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5310962009496486</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.2109889207668344</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.3842062771678397</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.404804802065326</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.2195321087945119</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4770547211034533</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3034131701020348</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2238014221922195</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5529034523966995</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2232951254110811</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2257353846715228</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6099142944457875</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1643503208826897</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1174882206176821</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.1875122583117055</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.6949995210706125</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1433367238493151</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3203718316540397</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5362914444966452</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1559029187325248</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.4352282212562546</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.4088688600112206</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.1621107558417982</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5314063647434991</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3064828794147027</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.1653218633546039</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6090202929223359</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2256578437230602</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1667449678205064</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6671896879661009</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1660653442133927</v>
+      </c>
+      <c r="G37" t="n">
         <v>1</v>
       </c>
     </row>

--- a/models/pt_sl_grid.xlsx
+++ b/models/pt_sl_grid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,19 +465,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5024972746637232</v>
+        <v>0.3860173328582217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00872563731817788</v>
+        <v>0.2443141882945997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.488777088018099</v>
+        <v>0.3696684788471786</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -488,19 +488,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6077203417275211</v>
+        <v>0.401349491488854</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03090234857849197</v>
+        <v>0.3204944212518757</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3613773096939869</v>
+        <v>0.2781560872592704</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -511,19 +511,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6595131340682999</v>
+        <v>0.4088717296571023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06474669196630162</v>
+        <v>0.3847162243006542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2757401739653985</v>
+        <v>0.2064120460422435</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -534,19 +534,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6854756681064956</v>
+        <v>0.4123958377602626</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1059118131354367</v>
+        <v>0.4358615594341813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2086125187580677</v>
+        <v>0.1517426028055562</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -557,19 +557,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.697877658628255</v>
+        <v>0.2885126498481495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1472456998982845</v>
+        <v>0.3261369171573066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1548766414734605</v>
+        <v>0.3853504329945439</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -580,19 +580,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7034788518466148</v>
+        <v>0.2995001520139395</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1817970342867829</v>
+        <v>0.4109770409914578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1147241138666022</v>
+        <v>0.2895228069946027</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -603,19 +603,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3717586743234552</v>
+        <v>0.3051818773231162</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03185564612135615</v>
+        <v>0.4803084738781208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5963856795551886</v>
+        <v>0.214509648798763</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -626,19 +626,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4615054803205634</v>
+        <v>0.3078364003099123</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08526311468306277</v>
+        <v>0.5345202407377743</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4532314049963738</v>
+        <v>0.1576433589523134</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -649,19 +649,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5067392206678556</v>
+        <v>0.2137904430634242</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1483312731767614</v>
+        <v>0.3932453504983769</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3449295061553829</v>
+        <v>0.392964206438199</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -672,19 +672,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5286376967601567</v>
+        <v>0.2217147826200665</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2123937803036869</v>
+        <v>0.483361829136332</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2589685229361564</v>
+        <v>0.2949233882436015</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -695,19 +695,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5390920411058252</v>
+        <v>0.2258698303001376</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2700523173340509</v>
+        <v>0.5556518128888206</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1908556415601239</v>
+        <v>0.2184783568110418</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -718,19 +718,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5438539675878835</v>
+        <v>0.2277168813931669</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3155734153138812</v>
+        <v>0.6116975543735882</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1405726170982353</v>
+        <v>0.160585564233245</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -741,19 +741,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" t="n">
-        <v>0.2796491500143679</v>
+        <v>0.1577054721749108</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06933529162238471</v>
+        <v>0.4455218001065732</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6510155583632474</v>
+        <v>0.396772727718516</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -764,19 +764,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3489981253335401</v>
+        <v>0.1634362342387698</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1522174430644183</v>
+        <v>0.5388616280856378</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4987844316020416</v>
+        <v>0.2977021376755924</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -787,19 +787,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3831663162119878</v>
+        <v>0.1664340145083411</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2367188319596422</v>
+        <v>0.6129823173462616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.38011485182837</v>
+        <v>0.2205836681453973</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -810,481 +810,21 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3990987005049284</v>
+        <v>0.1677155083640358</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3158242830883191</v>
+        <v>0.6701003292000798</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2850770164067524</v>
+        <v>0.1621841624358844</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.4069713873900173</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.3834035002896383</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.2096251123203445</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.4105975670387112</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.435168925236842</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.1542335077244468</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.2123071168906992</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.1115312512828466</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.6761616318264543</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.262726978320463</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2169869411920324</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5202860804875045</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="n">
-        <v>4</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.2869744890279558</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.3164582943728078</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.3965672165992364</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.2985463352779387</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4041616683163123</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.297291996405749</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.3044166411997865</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.4767810471677028</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.2188023116325106</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.3071396968605039</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.5319765187763126</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.1608837843631836</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.1579144221602908</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1531570569104949</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.6889285209292142</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.1936562381693038</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2752475608810476</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5310962009496486</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.2109889207668344</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.3842062771678397</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.404804802065326</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.2195321087945119</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.4770547211034533</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.3034131701020348</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.2238014221922195</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.5529034523966995</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.2232951254110811</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="n">
-        <v>6</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.2257353846715228</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.6099142944457875</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.1643503208826897</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="n">
-        <v>6</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.1174882206176821</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.1875122583117055</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.6949995210706125</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1433367238493151</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.3203718316540397</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.5362914444966452</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.1559029187325248</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.4352282212562546</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.4088688600112206</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.1621107558417982</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.5314063647434991</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.3064828794147027</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="n">
-        <v>6</v>
-      </c>
-      <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.1653218633546039</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.6090202929223359</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.2256578437230602</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" t="n">
-        <v>6</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.1667449678205064</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.6671896879661009</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.1660653442133927</v>
-      </c>
-      <c r="G37" t="n">
         <v>1</v>
       </c>
     </row>
